--- a/docs/oc-mensuales/desarrollo-y-mantencion-de-software-ti-e-iaas/jun-2026.xlsx
+++ b/docs/oc-mensuales/desarrollo-y-mantencion-de-software-ti-e-iaas/jun-2026.xlsx
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>28955.72</v>
+        <v>29271.92</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>18921.53</v>
+        <v>19128.15</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>28206.67</v>
+        <v>28514.69</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>21821.7</v>
+        <v>22060</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>15102.79</v>
+        <v>15267.72</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>431231.97</v>
+        <v>435941.1</v>
       </c>
     </row>
     <row r="8">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>29029.12</v>
+        <v>29283.71</v>
       </c>
     </row>
     <row r="9">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>17278.59</v>
+        <v>17430.13</v>
       </c>
     </row>
     <row r="10">
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>8753.950000000001</v>
+        <v>8830.73</v>
       </c>
     </row>
     <row r="11">
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>22871.66</v>
+        <v>23200.08</v>
       </c>
     </row>
     <row r="12">
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>253601.02</v>
+        <v>257242.59</v>
       </c>
     </row>
     <row r="13">
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>14143.64</v>
+        <v>14346.73</v>
       </c>
     </row>
     <row r="14">
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>63205.66</v>
+        <v>64113.26</v>
       </c>
     </row>
     <row r="15">
@@ -1362,7 +1362,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>38582.72</v>
+        <v>39136.74</v>
       </c>
     </row>
     <row r="16">
@@ -1423,7 +1423,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>30140.81</v>
+        <v>30383.54</v>
       </c>
     </row>
     <row r="17">
@@ -1484,7 +1484,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>19620.85</v>
+        <v>19778.86</v>
       </c>
     </row>
     <row r="18">
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>39487.71</v>
+        <v>39805.72</v>
       </c>
     </row>
     <row r="19">
@@ -1606,7 +1606,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>16450.21</v>
+        <v>16576.62</v>
       </c>
     </row>
     <row r="20">
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>32459.78</v>
+        <v>32199.67</v>
       </c>
     </row>
     <row r="21">
@@ -1732,7 +1732,7 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>10243.33</v>
+        <v>10070.27</v>
       </c>
     </row>
     <row r="22">
@@ -1793,7 +1793,7 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>31893.26</v>
+        <v>31442.28</v>
       </c>
     </row>
     <row r="23">
@@ -1854,7 +1854,7 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>29005.66</v>
+        <v>28831.2</v>
       </c>
     </row>
     <row r="24">
@@ -1915,7 +1915,7 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>37000.89</v>
+        <v>36778.34</v>
       </c>
     </row>
     <row r="25">
@@ -1976,7 +1976,7 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>11167.41</v>
+        <v>11222.46</v>
       </c>
     </row>
     <row r="26">
@@ -2037,7 +2037,7 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>53021.86</v>
+        <v>53835.73</v>
       </c>
     </row>
     <row r="27">
@@ -2098,7 +2098,7 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>10767.36</v>
+        <v>10932.63</v>
       </c>
     </row>
     <row r="28">
@@ -2159,7 +2159,7 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>11983.89</v>
+        <v>12167.84</v>
       </c>
     </row>
     <row r="29">
@@ -2220,7 +2220,7 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>41472.06</v>
+        <v>42282.45</v>
       </c>
     </row>
     <row r="30">
@@ -2281,7 +2281,7 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>15317.16</v>
+        <v>15616.46</v>
       </c>
     </row>
     <row r="31">
@@ -2342,7 +2342,7 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>89270.78</v>
+        <v>91015.17999999999</v>
       </c>
     </row>
     <row r="32">
@@ -2403,7 +2403,7 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>14981.44</v>
+        <v>15274.18</v>
       </c>
     </row>
     <row r="33">
@@ -2464,7 +2464,7 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>31303.04</v>
+        <v>31914.72</v>
       </c>
     </row>
     <row r="34">
@@ -2525,7 +2525,7 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>68123.78</v>
+        <v>69700.96000000001</v>
       </c>
     </row>
     <row r="35">
@@ -2586,7 +2586,7 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>16664.23</v>
+        <v>17050.03</v>
       </c>
     </row>
     <row r="36">
@@ -2647,7 +2647,7 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>39422.12</v>
+        <v>39720.2</v>
       </c>
     </row>
     <row r="37">
@@ -2708,7 +2708,7 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>32732.55</v>
+        <v>32980.05</v>
       </c>
     </row>
     <row r="38">
@@ -2769,7 +2769,7 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>32185.75</v>
+        <v>32429.11</v>
       </c>
     </row>
     <row r="39">
@@ -2830,7 +2830,7 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>37572.8</v>
+        <v>37721.09</v>
       </c>
     </row>
     <row r="40">
@@ -2891,7 +2891,7 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>39261.46</v>
+        <v>39416.42</v>
       </c>
     </row>
     <row r="41">
@@ -2952,7 +2952,7 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>8907.370000000001</v>
+        <v>8891.98</v>
       </c>
     </row>
     <row r="42">
@@ -3013,7 +3013,7 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>417776.85</v>
+        <v>412618.31</v>
       </c>
     </row>
     <row r="43">
@@ -3074,7 +3074,7 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>85040.11</v>
+        <v>83990.07000000001</v>
       </c>
     </row>
     <row r="44">
@@ -3135,7 +3135,7 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>133615.09</v>
+        <v>131137.6</v>
       </c>
     </row>
     <row r="45">
@@ -3196,7 +3196,7 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>18884.16</v>
+        <v>18625.2</v>
       </c>
     </row>
     <row r="46">
@@ -3257,7 +3257,7 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>29325.73</v>
+        <v>28923.58</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-mensuales/desarrollo-y-mantencion-de-software-ti-e-iaas/jun-2026.xlsx
+++ b/docs/oc-mensuales/desarrollo-y-mantencion-de-software-ti-e-iaas/jun-2026.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OC jun-2026" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="OC jun-2026" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1159,7 +1159,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1723,7 +1723,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">

--- a/docs/oc-mensuales/desarrollo-y-mantencion-de-software-ti-e-iaas/jun-2026.xlsx
+++ b/docs/oc-mensuales/desarrollo-y-mantencion-de-software-ti-e-iaas/jun-2026.xlsx
@@ -666,7 +666,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>MOP Dirección General de Concesiones</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA</t>
+          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE REDES ASISTENCIALES</t>
+          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1398,7 +1398,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Servicio de Salud del Reloncaví</t>
+          <t>SERVICIO SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1408,7 +1408,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>GEORG</t>
+          <t>Georg</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1652,7 +1652,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Transaction Line Chile S.A.</t>
+          <t>TRANSACTION LINE CHILE S.A.</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1829,7 +1829,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dirección General de Carabineros de Chile</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1880,7 +1880,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1900,7 +1900,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>SOLNET SPA</t>
+          <t>SolNet SPA</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1961,7 +1961,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>ZECOVERY LTDA   -    EXEC</t>
+          <t>Zecovery Ltda   -    EXEC</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2134,7 +2134,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Universidad de Chile</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2144,7 +2144,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>ZERVIZ</t>
+          <t>ZerviZ</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -2317,7 +2317,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2368,7 +2368,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -2378,7 +2378,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA SERENA</t>
+          <t>ILUSTRE MUNICIPALIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2449,7 +2449,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Asimov Consultores SpA</t>
+          <t>ASIMOV CONSULTORES SPA</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2510,7 +2510,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>VICTORIA SPA</t>
+          <t>VICTORIA SpA</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2683,7 +2683,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE ECONOMIA Y EMPRESAS DE MENOR TAMA</t>
+          <t>SUBSECRETARIA DE ECONOMIA Y EMPRESAS DE MENOR TAMANO</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2754,7 +2754,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>GEORG</t>
+          <t>Georg</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>ZERVIZ</t>
+          <t>ZerviZ</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">

--- a/docs/oc-mensuales/desarrollo-y-mantencion-de-software-ti-e-iaas/jun-2026.xlsx
+++ b/docs/oc-mensuales/desarrollo-y-mantencion-de-software-ti-e-iaas/jun-2026.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M46"/>
+  <dimension ref="A1:M48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -562,7 +562,11 @@
           <t>77.754.348-2</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -684,7 +688,11 @@
           <t>76.092.019-3</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -745,7 +753,11 @@
           <t>76.891.821-k</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
@@ -928,7 +940,11 @@
           <t>76.334.381-2</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1172,7 +1188,11 @@
           <t>76.286.397-9</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1185,7 +1205,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>1057415-2966-CM26</t>
+          <t>599-83-CM26</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1205,48 +1225,52 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>61.602.220-2</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD BIO BIO HOSPITAL NACIMIENTO</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>ANALYZE CONSULTORIA Y DESARROLLO SPA</t>
+          <t>NEURONET SOLUCIONES DE INGENIERIA Y TECNOLOGIA S.A.</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>77.592.300-8</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr"/>
+          <t>77.077.350-4</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>14346.73</v>
+        <v>39136.74</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2735-84-CM26</t>
+          <t>1057415-2966-CM26</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1266,32 +1290,32 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>69.255.200-8</t>
+          <t>61.602.220-2</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD LO BARNECHEA</t>
+          <t>SERVICIO SALUD BIO BIO HOSPITAL NACIMIENTO</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>LUUK SPA</t>
+          <t>ANALYZE CONSULTORIA Y DESARROLLO SPA</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>77.363.384-3</t>
+          <t>77.592.300-8</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -1301,13 +1325,13 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>64113.26</v>
+        <v>14346.73</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>599-83-CM26</t>
+          <t>2735-84-CM26</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1332,12 +1356,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>69.255.200-8</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>I MUNICIPALIDAD LO BARNECHEA</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1347,22 +1371,26 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>NEURONET SOLUCIONES DE INGENIERIA Y TECNOLOGIA S.A.</t>
+          <t>LUUK SPA</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>77.077.350-4</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr"/>
+          <t>77.363.384-3</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>39136.74</v>
+        <v>64113.26</v>
       </c>
     </row>
     <row r="16">
@@ -1416,7 +1444,11 @@
           <t>76.624.276-6</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1786,7 +1818,11 @@
           <t>77.146.212-K</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1799,7 +1835,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>699360-32-CM26</t>
+          <t>2291-1022-CM26</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1819,32 +1855,32 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>60.505.000-k</t>
+          <t>69.110.400-1</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>I MUNICIPALIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>NEURONET SOLUCIONES DE INGENIERIA Y TECNOLOGIA S.A.</t>
+          <t>SolNet SPA</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>77.077.350-4</t>
+          <t>96.723.130-4</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
@@ -1854,13 +1890,13 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>28831.2</v>
+        <v>36778.34</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2291-1022-CM26</t>
+          <t>699360-32-CM26</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1880,42 +1916,46 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>69.110.400-1</t>
+          <t>60.505.000-k</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALCA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>SolNet SPA</t>
+          <t>NEURONET SOLUCIONES DE INGENIERIA Y TECNOLOGIA S.A.</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>96.723.130-4</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr"/>
+          <t>77.077.350-4</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>36778.34</v>
+        <v>28831.2</v>
       </c>
     </row>
     <row r="25">
@@ -1969,7 +2009,11 @@
           <t>76.260.080-3</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2030,7 +2074,11 @@
           <t>76.304.354-1</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2091,7 +2139,11 @@
           <t>76.304.354-1</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2274,7 +2326,11 @@
           <t>77.077.350-4</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2287,7 +2343,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>621923-26-CM26</t>
+          <t>876-114-SE26</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2312,12 +2368,12 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>53.314.945-6</t>
+          <t>60.101.000-3</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>SECRETARIA GENERAL DE GOBIERNO</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2327,28 +2383,32 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>TIVIT CHILE TERCERIZACION DE PROCESOS, SERVICIOS Y TECNOLOGIA SPA</t>
+          <t>SERVICIOS TECNOLOGICOS ADEMANDA.COM LIMITADA</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>76.130.712-6</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr"/>
+          <t>76.093.443-7</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>91015.17999999999</v>
+        <v>178647.35</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2450-667-CM26</t>
+          <t>621923-26-CM26</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2373,27 +2433,27 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>69.040.100-2</t>
+          <t>53.314.945-6</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE LA SERENA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>IMPACTE SPA</t>
+          <t>TIVIT CHILE TERCERIZACION DE PROCESOS, SERVICIOS Y TECNOLOGIA SPA</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>76.572.009-5</t>
+          <t>76.130.712-6</t>
         </is>
       </c>
       <c r="K32" t="inlineStr"/>
@@ -2403,13 +2463,13 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>15274.18</v>
+        <v>91015.17999999999</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2083-2-CM26</t>
+          <t>2450-667-CM26</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2429,48 +2489,52 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>71.294.800-0</t>
+          <t>69.040.100-2</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>CENTRO DE INFORMACION DE RECURSOS NATURALES</t>
+          <t>ILUSTRE MUNICIPALIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>ASIMOV CONSULTORES SPA</t>
+          <t>IMPACTE SPA</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>76.372.725-4</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr"/>
+          <t>76.572.009-5</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>31914.72</v>
+        <v>15274.18</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>1375753-86-CM26</t>
+          <t>2083-2-CM26</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2485,7 +2549,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2495,12 +2559,12 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>61.981.290-5</t>
+          <t>71.294.800-0</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA LOS ANDES</t>
+          <t>CENTRO DE INFORMACION DE RECURSOS NATURALES</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2510,12 +2574,12 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>VICTORIA SpA</t>
+          <t>ASIMOV CONSULTORES SPA</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>76.188.587-1</t>
+          <t>76.372.725-4</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
@@ -2525,7 +2589,7 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>69700.96000000001</v>
+        <v>31914.72</v>
       </c>
     </row>
     <row r="35">
@@ -2592,7 +2656,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>907581-18-CM26</t>
+          <t>1375753-86-CM26</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2607,7 +2671,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2617,43 +2681,47 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>60.921.000-1</t>
+          <t>61.981.290-5</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE VALPARAISO</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA LOS ANDES</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>NEURONET SOLUCIONES DE INGENIERIA Y TECNOLOGIA S.A.</t>
+          <t>VICTORIA SpA</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>77.077.350-4</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr"/>
+          <t>76.188.587-1</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>39720.2</v>
+        <v>69700.96000000001</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>756-149-CM26</t>
+          <t>2320-223-CM26</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2678,43 +2746,47 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>60.701.000-5</t>
+          <t>69.130.100-1</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE ECONOMIA Y EMPRESAS DE MENOR TAMANO</t>
+          <t>I MUNICIPALIDAD DE SAN JAVIER</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>SAARGO SPA</t>
+          <t>Georg</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>76.891.821-k</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr"/>
+          <t>76.624.276-6</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>32980.05</v>
+        <v>32429.11</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2320-223-CM26</t>
+          <t>907581-18-CM26</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2739,43 +2811,47 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>69.130.100-1</t>
+          <t>60.921.000-1</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN JAVIER</t>
+          <t>UNIVERSIDAD DE VALPARAISO</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Georg</t>
+          <t>NEURONET SOLUCIONES DE INGENIERIA Y TECNOLOGIA S.A.</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>76.624.276-6</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr"/>
+          <t>77.077.350-4</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>32429.11</v>
+        <v>39720.2</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2345-251-CM26</t>
+          <t>756-149-CM26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2790,7 +2866,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2800,12 +2876,12 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>69.070.400-5</t>
+          <t>60.701.000-5</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LAS CONDES</t>
+          <t>SUBSECRETARIA DE ECONOMIA Y EMPRESAS DE MENOR TAMANO</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2815,28 +2891,32 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>BELL TECHNOLOGIES SOCIEDAD ANÓNIMA</t>
+          <t>SAARGO SPA</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>96.847.780-3</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr"/>
+          <t>76.891.821-k</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L39" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>37721.09</v>
+        <v>32980.05</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>758-447-CM26</t>
+          <t>2345-251-CM26</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2861,12 +2941,12 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>60.509.001-k</t>
+          <t>69.070.400-5</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
+          <t>I MUNICIPALIDAD DE LAS CONDES</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2876,12 +2956,12 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>ZerviZ</t>
+          <t>BELL TECHNOLOGIES SOCIEDAD ANÓNIMA</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>76.755.489-3</t>
+          <t>96.847.780-3</t>
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
@@ -2891,13 +2971,13 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>39416.42</v>
+        <v>37721.09</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>3082-271-CM26</t>
+          <t>758-447-CM26</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2912,7 +2992,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2922,27 +3002,27 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>69.050.800-1</t>
+          <t>60.509.001-k</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PANQUEHUE</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>TICHILE  REVENTA  DE SOFTWARE Y HARDWARE SPA</t>
+          <t>ZerviZ</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>76.334.381-2</t>
+          <t>76.755.489-3</t>
         </is>
       </c>
       <c r="K41" t="inlineStr"/>
@@ -2952,13 +3032,13 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>8891.98</v>
+        <v>39416.42</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>538598-2171-CM26</t>
+          <t>3082-271-CM26</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2973,7 +3053,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2983,43 +3063,47 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>61.979.450-8</t>
+          <t>69.050.800-1</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>HOSPITAL METROPOLITANO DE SANTIAGO</t>
+          <t>I MUNICIPALIDAD DE PANQUEHUE</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>SISTEMAS EXPERTOS E INGENIERIA DE SOFTWARE LIMITADA</t>
+          <t>TICHILE  REVENTA  DE SOFTWARE Y HARDWARE SPA</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>76.132.093-9</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr"/>
+          <t>76.334.381-2</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L42" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>412618.31</v>
+        <v>8891.98</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2268-97-CM26</t>
+          <t>2036-296-SE26</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3034,53 +3118,57 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>61.608.700-2</t>
+          <t>61.602.247-4</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>CENTRAL DE ABASTECIMIENTO DEL SISTEMA NACIONAL DE SERVICIO DE SALUD</t>
+          <t>SERVICIO DE SALUD DE LA ARAUCANIA SUR HOSPITAL LONCOCHE</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>AQUANTA INGENIERIA COMPUTACIONAL SPA</t>
+          <t>Georg</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>77.842.230-1</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr"/>
+          <t>76.624.276-6</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L43" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>83990.07000000001</v>
+        <v>15302.29</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>45-57-CM26</t>
+          <t>538598-2171-CM26</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3095,22 +3183,22 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>61.531.000-K</t>
+          <t>61.979.450-8</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE CAPACITACION Y EMPLEO</t>
+          <t>HOSPITAL METROPOLITANO DE SANTIAGO</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3120,12 +3208,12 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>XMS TECHNOLOGIES S.A.</t>
+          <t>SISTEMAS EXPERTOS E INGENIERIA DE SOFTWARE LIMITADA</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>76.083.145-k</t>
+          <t>76.132.093-9</t>
         </is>
       </c>
       <c r="K44" t="inlineStr"/>
@@ -3135,13 +3223,13 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>131137.6</v>
+        <v>412618.31</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>765-144-CM26</t>
+          <t>2268-97-CM26</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3156,7 +3244,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -3166,97 +3254,231 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>72.396.000-2</t>
+          <t>61.608.700-2</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>CORP NACIONAL DE DESARROLLO INDIGENA</t>
+          <t>CENTRAL DE ABASTECIMIENTO DEL SISTEMA NACIONAL DE SERVICIO DE SALUD</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>SAARGO SPA</t>
+          <t>AQUANTA INGENIERIA COMPUTACIONAL SPA</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>76.891.821-k</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr"/>
+          <t>77.842.230-1</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L45" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>18625.2</v>
+        <v>83990.07000000001</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
+          <t>45-57-CM26</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>61.531.000-K</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE CAPACITACION Y EMPLEO</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>XMS TECHNOLOGIES S.A.</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>76.083.145-k</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="n">
+        <v>131137.6</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>765-144-CM26</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>72.396.000-2</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>CORP NACIONAL DE DESARROLLO INDIGENA</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>SAARGO SPA</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>76.891.821-k</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="n">
+        <v>18625.2</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
           <t>1221016-6449-CM26</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>2239-19-LR23</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>jun-2026</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
         <is>
           <t>2026-06-26</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
+      <c r="E48" t="inlineStr">
         <is>
           <t>Aceptada</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
+      <c r="F48" t="inlineStr">
         <is>
           <t>71.378.000-6</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr">
+      <c r="G48" t="inlineStr">
         <is>
           <t>Corporación de Desarrollo de La Reina</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
         <is>
           <t>SERVICIOS INFORMÁTICOS COMMUNITY MARKETPLACE LIMITADA</t>
         </is>
       </c>
-      <c r="J46" t="inlineStr">
+      <c r="J48" t="inlineStr">
         <is>
           <t>76.802.163-5</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M46" s="2" t="n">
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="n">
         <v>28923.58</v>
       </c>
     </row>

--- a/docs/oc-mensuales/desarrollo-y-mantencion-de-software-ti-e-iaas/jun-2026.xlsx
+++ b/docs/oc-mensuales/desarrollo-y-mantencion-de-software-ti-e-iaas/jun-2026.xlsx
@@ -851,7 +851,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1038,7 +1038,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1542,7 +1542,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1725,7 +1725,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1916,7 +1916,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -2046,7 +2046,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -2111,7 +2111,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -2237,7 +2237,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -2554,7 +2554,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -2615,7 +2615,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -2676,7 +2676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -2741,7 +2741,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -2997,7 +2997,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
